--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,6 +909,2469 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126493498</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>751306</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7197196</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126493497</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>751337</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7197181</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126493495</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7197197</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126493481</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>751161</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7197278</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126493501</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>751227</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7197146</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126493496</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>751345</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7197196</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126493486</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91611</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>751169</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7197212</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126493503</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91655</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>751685</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7197107</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126493491</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>751515</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7197144</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126493474</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>751389</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7197186</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126493502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>751172</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7197276</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126493489</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>751673</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7197134</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126493475</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>751292</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7197164</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126493500</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>751282</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7197144</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126493499</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>751291</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7197141</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126493494</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>751363</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7197197</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126493478</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91603</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>751158</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7197277</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126493492</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>751456</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7197157</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126493482</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>112</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>751448</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7197159</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126493490</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>751574</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7197198</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126493487</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91611</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>751141</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7197268</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126493488</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>751433</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7197173</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126493493</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>751358</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7197214</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126493477</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>751172</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7197276</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126493479</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Loberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>751295</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7197155</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126493498</v>
+        <v>126493497</v>
       </c>
       <c r="B4" t="n">
         <v>78980</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751306</v>
+        <v>751337</v>
       </c>
       <c r="R4" t="n">
-        <v>7197196</v>
+        <v>7197181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126493497</v>
+        <v>126493498</v>
       </c>
       <c r="B5" t="n">
         <v>78980</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751337</v>
+        <v>751306</v>
       </c>
       <c r="R5" t="n">
-        <v>7197181</v>
+        <v>7197196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126493496</v>
+        <v>126493486</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>91611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,34 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2064</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751345</v>
+        <v>751169</v>
       </c>
       <c r="R9" t="n">
-        <v>7197196</v>
+        <v>7197212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,6 +1488,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126493486</v>
+        <v>126493491</v>
       </c>
       <c r="B10" t="n">
-        <v>91611</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1514,37 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2064</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751169</v>
+        <v>751515</v>
       </c>
       <c r="R10" t="n">
-        <v>7197212</v>
+        <v>7197144</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,18 +1580,12 @@
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1706,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126493491</v>
+        <v>126493496</v>
       </c>
       <c r="B12" t="n">
         <v>78980</v>
@@ -1741,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751515</v>
+        <v>751345</v>
       </c>
       <c r="R12" t="n">
-        <v>7197144</v>
+        <v>7197196</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1772,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2288,7 +2288,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126493499</v>
+        <v>126493494</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751291</v>
+        <v>751363</v>
       </c>
       <c r="R18" t="n">
-        <v>7197141</v>
+        <v>7197197</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,6 +2359,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2385,7 +2390,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126493494</v>
+        <v>126493499</v>
       </c>
       <c r="B19" t="n">
         <v>78980</v>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751363</v>
+        <v>751291</v>
       </c>
       <c r="R19" t="n">
-        <v>7197197</v>
+        <v>7197141</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,11 +2461,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126493492</v>
+        <v>126493482</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>91195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751456</v>
+        <v>751448</v>
       </c>
       <c r="R21" t="n">
-        <v>7197157</v>
+        <v>7197159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126493482</v>
+        <v>126493492</v>
       </c>
       <c r="B22" t="n">
-        <v>91195</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751448</v>
+        <v>751456</v>
       </c>
       <c r="R22" t="n">
-        <v>7197159</v>
+        <v>7197157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126493488</v>
+        <v>126493493</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751433</v>
+        <v>751358</v>
       </c>
       <c r="R25" t="n">
-        <v>7197173</v>
+        <v>7197214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,6 +3052,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,7 +3083,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126493493</v>
+        <v>126493488</v>
       </c>
       <c r="B26" t="n">
         <v>78980</v>
@@ -3113,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751358</v>
+        <v>751433</v>
       </c>
       <c r="R26" t="n">
-        <v>7197214</v>
+        <v>7197173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,11 +3154,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -2487,32 +2487,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126493478</v>
+        <v>126493492</v>
       </c>
       <c r="B20" t="n">
-        <v>91603</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751158</v>
+        <v>751456</v>
       </c>
       <c r="R20" t="n">
-        <v>7197277</v>
+        <v>7197157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2584,32 +2584,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126493482</v>
+        <v>126493478</v>
       </c>
       <c r="B21" t="n">
-        <v>91195</v>
+        <v>91603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751448</v>
+        <v>751158</v>
       </c>
       <c r="R21" t="n">
-        <v>7197159</v>
+        <v>7197277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126493492</v>
+        <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>91195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751456</v>
+        <v>751448</v>
       </c>
       <c r="R22" t="n">
-        <v>7197157</v>
+        <v>7197159</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -2487,32 +2487,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126493492</v>
+        <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>91603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751456</v>
+        <v>751158</v>
       </c>
       <c r="R20" t="n">
-        <v>7197157</v>
+        <v>7197277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2584,32 +2584,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126493478</v>
+        <v>126493482</v>
       </c>
       <c r="B21" t="n">
-        <v>91603</v>
+        <v>91195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751158</v>
+        <v>751448</v>
       </c>
       <c r="R21" t="n">
-        <v>7197277</v>
+        <v>7197159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126493482</v>
+        <v>126493492</v>
       </c>
       <c r="B22" t="n">
-        <v>91195</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751448</v>
+        <v>751456</v>
       </c>
       <c r="R22" t="n">
-        <v>7197159</v>
+        <v>7197157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,14 +1004,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,14 +1105,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,14 +1211,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,14 +1312,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,14 +1413,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,14 +1514,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,14 +1620,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91611</v>
+        <v>91870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,14 +1730,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91655</v>
+        <v>91914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,14 +1831,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91210</v>
+        <v>91469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,14 +1932,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,14 +2033,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,14 +2134,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91210</v>
+        <v>91469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,14 +2235,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,14 +2336,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2381,14 +2437,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,14 +2543,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91603</v>
+        <v>91862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,14 +2644,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2677,14 +2745,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91195</v>
+        <v>91454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2774,14 +2846,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,14 +2947,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91611</v>
+        <v>91870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,14 +3057,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,14 +3163,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3176,14 +3264,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91210</v>
+        <v>91469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3273,14 +3365,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91245</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3370,7 +3466,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91914</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91874</v>
+        <v>91879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91874</v>
+        <v>91879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91887</v>
+        <v>91890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91887</v>
+        <v>91890</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91893</v>
+        <v>91900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91893</v>
+        <v>91900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91900</v>
+        <v>91907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91900</v>
+        <v>91907</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91907</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91907</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91909</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>91919</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>91919</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91919</v>
+        <v>91922</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91919</v>
+        <v>91922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>126493498</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>126493497</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>126493495</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>126493501</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>126493491</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>126493496</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91966</v>
+        <v>91968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>126493502</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>126493500</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>126493499</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>126493494</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>126493492</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>126493490</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>126493493</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>126493488</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>126493481</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126493486</v>
       </c>
       <c r="B11" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126493503</v>
       </c>
       <c r="B12" t="n">
-        <v>91968</v>
+        <v>91972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126493474</v>
       </c>
       <c r="B13" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>126493475</v>
       </c>
       <c r="B16" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126493478</v>
       </c>
       <c r="B20" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>126493482</v>
       </c>
       <c r="B22" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>126493487</v>
       </c>
       <c r="B24" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126493477</v>
       </c>
       <c r="B27" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>126493479</v>
       </c>
       <c r="B28" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63657979</v>
+        <v>126493482</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmselet 4, Vb</t>
+          <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751494.9240852073</v>
+        <v>751448</v>
       </c>
       <c r="R2" t="n">
-        <v>7197217.115187421</v>
+        <v>7197159</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63658013</v>
+        <v>126493479</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,43 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmselet 4, Vb</t>
+          <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751494.9240852073</v>
+        <v>751295</v>
       </c>
       <c r="R3" t="n">
-        <v>7197217.115187421</v>
+        <v>7197155</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-06-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-06-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126493498</v>
+        <v>126493481</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751306</v>
+        <v>751161</v>
       </c>
       <c r="R4" t="n">
-        <v>7197196</v>
+        <v>7197278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126493497</v>
+        <v>63658185</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,37 +989,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Loberg, Vb</t>
+          <t>Holmselet 4, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751337</v>
+        <v>751478</v>
       </c>
       <c r="R5" t="n">
-        <v>7197181</v>
+        <v>7197228</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,12 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2010-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2010-06-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,54 +1063,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126493495</v>
+        <v>126493478</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>92281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751354</v>
+        <v>751158</v>
       </c>
       <c r="R6" t="n">
-        <v>7197197</v>
+        <v>7197277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1153,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,45 +1183,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126493481</v>
+        <v>126493486</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>92289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2064</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751161</v>
+        <v>751169</v>
       </c>
       <c r="R7" t="n">
-        <v>7197278</v>
+        <v>7197212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,12 +1259,18 @@
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,45 +1293,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126493501</v>
+        <v>126493487</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>92289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2064</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751227</v>
+        <v>751141</v>
       </c>
       <c r="R8" t="n">
-        <v>7197146</v>
+        <v>7197268</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,12 +1369,18 @@
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,32 +1403,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126493491</v>
+        <v>126493503</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751515</v>
+        <v>751685</v>
       </c>
       <c r="R9" t="n">
-        <v>7197144</v>
+        <v>7197107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,32 +1504,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126493496</v>
+        <v>126493474</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751345</v>
+        <v>751389</v>
       </c>
       <c r="R10" t="n">
-        <v>7197196</v>
+        <v>7197186</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,11 +1575,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,48 +1605,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126493486</v>
+        <v>126493475</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2064</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751169</v>
+        <v>751292</v>
       </c>
       <c r="R11" t="n">
-        <v>7197212</v>
+        <v>7197164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,18 +1678,12 @@
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1738,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126493503</v>
+        <v>126493477</v>
       </c>
       <c r="B12" t="n">
-        <v>91972</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751685</v>
+        <v>751172</v>
       </c>
       <c r="R12" t="n">
-        <v>7197107</v>
+        <v>7197276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,48 +1807,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126493474</v>
+        <v>63658013</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Loberg, Vb</t>
+          <t>Holmselet 4, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751389</v>
+        <v>751495</v>
       </c>
       <c r="R13" t="n">
-        <v>7197186</v>
+        <v>7197217</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,12 +1878,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2010-06-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2010-06-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,30 +1898,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126493502</v>
+        <v>126493488</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1975,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751172</v>
+        <v>751433</v>
       </c>
       <c r="R14" t="n">
-        <v>7197276</v>
+        <v>7197173</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,11 +2014,11 @@
         <v>126493489</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2142,32 +2112,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126493475</v>
+        <v>126493490</v>
       </c>
       <c r="B16" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751292</v>
+        <v>751574</v>
       </c>
       <c r="R16" t="n">
-        <v>7197164</v>
+        <v>7197198</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,14 +2213,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126493500</v>
+        <v>126493491</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2278,7 +2248,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751282</v>
+        <v>751515</v>
       </c>
       <c r="R17" t="n">
         <v>7197144</v>
@@ -2344,14 +2314,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126493499</v>
+        <v>126493492</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2379,10 +2349,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751291</v>
+        <v>751456</v>
       </c>
       <c r="R18" t="n">
-        <v>7197141</v>
+        <v>7197157</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,14 +2415,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126493494</v>
+        <v>126493493</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2480,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751363</v>
+        <v>751358</v>
       </c>
       <c r="R19" t="n">
-        <v>7197197</v>
+        <v>7197214</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126493478</v>
+        <v>126493494</v>
       </c>
       <c r="B20" t="n">
-        <v>91920</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751158</v>
+        <v>751363</v>
       </c>
       <c r="R20" t="n">
-        <v>7197277</v>
+        <v>7197197</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,6 +2592,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,14 +2627,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126493492</v>
+        <v>126493495</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2687,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751456</v>
+        <v>751354</v>
       </c>
       <c r="R21" t="n">
-        <v>7197157</v>
+        <v>7197197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,6 +2698,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2753,32 +2733,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126493482</v>
+        <v>126493496</v>
       </c>
       <c r="B22" t="n">
-        <v>91500</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2788,10 +2768,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751448</v>
+        <v>751345</v>
       </c>
       <c r="R22" t="n">
-        <v>7197159</v>
+        <v>7197196</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2824,6 +2804,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2854,14 +2839,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126493490</v>
+        <v>126493497</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2889,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751574</v>
+        <v>751337</v>
       </c>
       <c r="R23" t="n">
-        <v>7197198</v>
+        <v>7197181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2955,48 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126493487</v>
+        <v>126493498</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2064</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Loberg, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751141</v>
+        <v>751306</v>
       </c>
       <c r="R24" t="n">
-        <v>7197268</v>
+        <v>7197196</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,18 +3013,12 @@
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Skeletocutis på/strax bredvid döda fruktkroppar av violticka</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3065,14 +3041,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126493493</v>
+        <v>126493499</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3100,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751358</v>
+        <v>751291</v>
       </c>
       <c r="R25" t="n">
-        <v>7197214</v>
+        <v>7197141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,11 +3112,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3171,14 +3142,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126493488</v>
+        <v>126493500</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3206,10 +3177,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751433</v>
+        <v>751282</v>
       </c>
       <c r="R26" t="n">
-        <v>7197173</v>
+        <v>7197144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,32 +3243,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126493477</v>
+        <v>126493501</v>
       </c>
       <c r="B27" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751172</v>
+        <v>751227</v>
       </c>
       <c r="R27" t="n">
-        <v>7197276</v>
+        <v>7197146</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,32 +3344,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126493479</v>
+        <v>126493502</v>
       </c>
       <c r="B28" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3379,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751295</v>
+        <v>751172</v>
       </c>
       <c r="R28" t="n">
-        <v>7197155</v>
+        <v>7197276</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,6 +3442,417 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>63657909</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Holmselet 4, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>751532</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7197245</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2010-06-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2010-06-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>63657979</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Holmselet 4, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>751495</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7197217</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2010-06-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2010-06-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>63658146</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Holmselet 4, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>751478</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7197228</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2010-06-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2010-06-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>99021935</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Finnfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>751049</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7197019</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I vägdiket</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jonas Muntlin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jonas Muntlin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26112-2025 artfynd.xlsx
+++ b/artfynd/A 26112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493479</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63658185</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493478</t>
         </is>
       </c>
     </row>
@@ -1290,6 +1320,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493486</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493487</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493474</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493475</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493477</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63658013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493488</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2109,6 +2179,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493489</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493490</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2311,6 +2391,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493491</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2412,6 +2497,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493492</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2518,6 +2608,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493493</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2624,6 +2719,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493494</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493495</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2836,6 +2941,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493496</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2937,6 +3047,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493497</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493498</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3139,6 +3259,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493499</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3240,6 +3365,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493500</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3341,6 +3471,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493501</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3442,6 +3577,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493502</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3541,6 +3681,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63657909</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3644,6 +3789,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63657979</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3747,6 +3897,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63658146</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3853,8 +4008,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99021935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>